--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_28.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_28.xlsx
@@ -9610,8 +9610,8 @@
       <c r="K212" s="13">
         <v>0</v>
       </c>
-      <c r="L212" s="13">
-        <v>0</v>
+      <c r="L212" s="14">
+        <v>1</v>
       </c>
       <c r="M212" s="13">
         <v>0</v>
@@ -24624,8 +24624,8 @@
       <c r="K212" s="13">
         <v>0</v>
       </c>
-      <c r="L212" s="13">
-        <v>0</v>
+      <c r="L212" s="14">
+        <v>1</v>
       </c>
       <c r="M212" s="13">
         <v>0</v>
@@ -39638,8 +39638,8 @@
       <c r="K212" s="13">
         <v>0</v>
       </c>
-      <c r="L212" s="13">
-        <v>0</v>
+      <c r="L212" s="14">
+        <v>1</v>
       </c>
       <c r="M212" s="13">
         <v>0</v>
